--- a/pm/route-days-v2/Spine-Route-Days-Coty.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Coty.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -17987,7 +17987,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -18017,7 +18017,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -18047,7 +18047,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -18077,7 +18077,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -18107,7 +18107,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -18137,7 +18137,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -18167,7 +18167,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -18197,7 +18197,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -18227,7 +18227,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -18257,7 +18257,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -18287,7 +18287,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -18317,7 +18317,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -18347,7 +18347,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -18377,7 +18377,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -18407,7 +18407,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -18437,7 +18437,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -18467,7 +18467,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -18497,7 +18497,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -18527,7 +18527,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -18557,7 +18557,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -18587,7 +18587,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -18617,7 +18617,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -18647,7 +18647,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -18677,7 +18677,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -18707,7 +18707,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -18737,7 +18737,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -18767,7 +18767,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -18797,7 +18797,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -18827,7 +18827,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -18857,7 +18857,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -18887,7 +18887,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -18917,7 +18917,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -18947,7 +18947,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -18977,7 +18977,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -19007,7 +19007,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -19037,7 +19037,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -19067,7 +19067,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -19097,7 +19097,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -19127,7 +19127,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -19157,7 +19157,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -19187,7 +19187,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -19217,7 +19217,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -19247,7 +19247,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -19277,7 +19277,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -19307,7 +19307,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -19337,7 +19337,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -19367,7 +19367,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -19397,7 +19397,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -19427,7 +19427,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -19457,7 +19457,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -19487,7 +19487,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -19517,7 +19517,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -19547,7 +19547,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -19577,7 +19577,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -19607,7 +19607,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -19637,7 +19637,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -19667,7 +19667,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -19697,7 +19697,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -19727,7 +19727,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -19757,7 +19757,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -19787,7 +19787,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -19817,7 +19817,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -19847,7 +19847,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -19877,7 +19877,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -19907,7 +19907,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -19937,7 +19937,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -19967,7 +19967,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -19997,7 +19997,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -20027,7 +20027,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -20057,7 +20057,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -20087,7 +20087,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -20117,7 +20117,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -20147,7 +20147,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -20177,7 +20177,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">

--- a/pm/route-days-v2/Spine-Route-Days-Coty.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Coty.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,11 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
     </font>
     <font>
       <i val="1"/>
@@ -96,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -120,13 +125,19 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1013,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1148,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1238,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1283,7 +1294,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1328,7 +1339,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1373,7 +1384,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1418,7 +1429,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1463,7 +1474,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1508,7 +1519,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1553,7 +1564,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1598,7 +1609,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -1643,7 +1654,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -1688,7 +1699,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -1733,7 +1744,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -1778,7 +1789,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -1823,7 +1834,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -17934,21 +17945,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cycle 2 plan. First pass = the full day. Cadence revisit / Producer sweep = the producing accounts only (2–4 quick stops). Pick the weekday at the Monday huddle.</t>
+          <t>5 route-day slots per week. First pass = the full day. Cadence revisit = the producers due on rhythm, packed into one full loop day (a label like R03+R07 = one drive covering both days’ producers). Open slots are flex. Pick weekdays at the Monday huddle.</t>
         </is>
       </c>
     </row>
@@ -17965,7 +17976,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Route Day</t>
+          <t>Route Day(s)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -17995,7 +18006,7 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>C-R03</t>
         </is>
@@ -18025,7 +18036,7 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>C-R04</t>
         </is>
@@ -18055,7 +18066,7 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>C-R06</t>
         </is>
@@ -18085,7 +18096,7 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>C-R09</t>
         </is>
@@ -18107,30 +18118,30 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>C-R01</t>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>C-R10</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Chronic Pain Institute · The Family Doctor · Henry Ford Macomb Internal Medicine · DMC Orthopedics &amp; Sports Medicine - Warren · Office of Steven Trombly MD · Macomb Physicians Group</t>
+          <t>Trinity IHA Orthopedics - Brighton, · Core Institute - Brighton · Restorative Physical Medicine - Brighton · Lederman Kwartowitz - Brighton · Providence Family &amp; Athletic Medicine · Oakland Internal Medicine Associates - Henry Ford · Prime Internal Medicine (MDVIP) · DMC Primary and Specialty Care - Milford · North Valley Internal Medicine</t>
         </is>
       </c>
     </row>
@@ -18145,9 +18156,9 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>C-R05</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>C-R01</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -18156,11 +18167,11 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Preferred Medical Group · Be Well Medical Center</t>
+          <t>Chronic Pain Institute · The Family Doctor · Henry Ford Macomb Internal Medicine · DMC Orthopedics &amp; Sports Medicine - Warren · Office of Steven Trombly MD · Macomb Physicians Group</t>
         </is>
       </c>
     </row>
@@ -18175,9 +18186,9 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>C-R07</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>C-R05+R07</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -18186,11 +18197,11 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Epic Primary Care - Ferndale · Madison Medical Arts · Barry S Meyer DO PC</t>
+          <t>Preferred Medical Group · Be Well Medical Center · Epic Primary Care - Ferndale · Madison Medical Arts · Barry S Meyer DO PC</t>
         </is>
       </c>
     </row>
@@ -18205,9 +18216,9 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>C-R10</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>C-R11</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -18216,11 +18227,11 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Trinity IHA Orthopedics - Brighton, · Core Institute - Brighton · Restorative Physical Medicine - Brighton · Lederman Kwartowitz - Brighton · Providence Family &amp; Athletic Medicine · Oakland Internal Medicine Associates - Henry Ford · Prime Internal Medicine (MDVIP) · DMC Primary and Specialty Care - Milford · North Valley Internal Medicine</t>
+          <t>Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD · Corewell Health Medical Group East · Michigan Surgery Specialists  - Roseville · Michigan Institute for Neurological Disorders (MIND) - Roseville · Corewell Health Family Medicine -SAINT CLAIR SHORES · Premier Orthopedics &amp; Sports Medicine · Henry Ford Health Medical Center (Ascension) · Shores Internal Medicine · ESSENTIAL CARE FAMILY MEDICINE</t>
         </is>
       </c>
     </row>
@@ -18235,9 +18246,9 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>C-R11</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>C-R12</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -18250,7 +18261,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD · Corewell Health Medical Group East · Michigan Surgery Specialists  - Roseville · Michigan Institute for Neurological Disorders (MIND) - Roseville · Corewell Health Family Medicine -SAINT CLAIR SHORES · Premier Orthopedics &amp; Sports Medicine · Henry Ford Health Medical Center (Ascension) · Shores Internal Medicine · ESSENTIAL CARE FAMILY MEDICINE</t>
+          <t>Emil Sitto MD · McLaren Macomb Primary Care · Romeo Plank Family Practice · Cornerstone Internal Medicine · Silver Pine Medical Group Romeo Plank · Neuro Pain Consultants - Macomb · Frederick Karoub MD PC · Epic Healthcare - Southfield · Medpointe urgent care - St Clair Shores · Belamedica</t>
         </is>
       </c>
     </row>
@@ -18265,9 +18276,9 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>C-R12</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>C-R13</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -18276,11 +18287,11 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Emil Sitto MD · McLaren Macomb Primary Care · Romeo Plank Family Practice · Cornerstone Internal Medicine · Silver Pine Medical Group Romeo Plank · Neuro Pain Consultants - Macomb · Frederick Karoub MD PC · Epic Healthcare - Southfield · Medpointe urgent care - St Clair Shores · Belamedica</t>
+          <t>Regenerative Pain Medicine · MDVIP - Troy · Bones &amp; Joints Clinic · Hope Medical Center · Changee Kim MD · Precise Chiropractic · Office of Josephine A. Iskander MD · Forum Medical Clinic</t>
         </is>
       </c>
     </row>
@@ -18295,7 +18306,7 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>C-R01</t>
         </is>
@@ -18325,9 +18336,9 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>C-R02</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>C-R02+R05+R07+R08</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -18336,11 +18347,11 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Lakeview Medical Center · Gratiot Family Medicine</t>
+          <t>Lakeview Medical Center · Gratiot Family Medicine · Troy Primary Care · Progressive Health Care · John R Medical Clinic · MHP Internal Medicine · Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates</t>
         </is>
       </c>
     </row>
@@ -18355,22 +18366,22 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>C-R05</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>C-R14</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Troy Primary Care · Progressive Health Care</t>
+          <t>Troy Health Center · Detroit Ortho Institute · Macomb Medical Clinic · Farrah Ahmad MD · AS Medical Group · Mi Family Medicine &amp; Urgent Care · Oakland Macomb Surgical Group - Madison Heights · Saurabh Gupta MD</t>
         </is>
       </c>
     </row>
@@ -18385,22 +18396,22 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>C-R07</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>C-R15</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>John R Medical Clinic · MHP Internal Medicine</t>
+          <t>ANDERSON SPORTS MEDICINE · Neurology Consultants of Southfield · EPIC Southfield - Telegraph Rd office · Michigan Neurology Associates - Clinton Township · Normandy Family Practice · Michigan MSK Medicine - Clinton Township · Multi-Specialty Clinic · Albert Przybylski DO · Center for Orthopedic Surgery · St Clair Orthpaedics &amp; Sports Medicine - Macomb</t>
         </is>
       </c>
     </row>
@@ -18415,69 +18426,69 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>C-R08</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>C-R16</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates</t>
+          <t>Corewell Center for Pain Management · Arcturus Healthcare - Rochester Hills · Rochester Medical Group · Phase Family Medicine · Rochester Family Medicine Center · Stamatin Internal Medicine · Rochester Internists · Corewell Internal Medicine Midway · Rochester Family Practice</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>C-R13</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>C-R02+R03+R04+R06+R09+R10</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Cadence revisit</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Regenerative Pain Medicine · MDVIP - Troy · Bones &amp; Joints Clinic · Hope Medical Center · Changee Kim MD · Precise Chiropractic · Office of Josephine A. Iskander MD · Forum Medical Clinic</t>
+          <t>Premier Family Physicians · Shaun Jayakar MD · Office of George Nassif MD · Oak Street Health - Eastgate · Oakland Primary Care · Faith Internal Medicine &amp; Urgent Care · MEDPRO PRIMARY CARE - Waltz Rd · Schoenherr Family Practice · North Valley Internal Medicine</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>C-R14</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>C-R17</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -18490,7 +18501,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Troy Health Center · Detroit Ortho Institute · Macomb Medical Clinic · Farrah Ahmad MD · AS Medical Group · Mi Family Medicine &amp; Urgent Care · Oakland Macomb Surgical Group - Madison Heights · Saurabh Gupta MD</t>
+          <t>Premiere Pediatrics · HARTLAND PEDIATRICS · Michigan Institute for Neurological Disorders (MIND) - Farmington Hills · Jagannathan Neurosurgery · CarePoint Internal Medicine · AMG Oak Park Medical Center · Greater Michigan Orthopedics · Flint Children’s Center</t>
         </is>
       </c>
     </row>
@@ -18505,22 +18516,22 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>C-R02</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>C-R18</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Premier Family Physicians · Shaun Jayakar MD</t>
+          <t>Raad Kasmikha MD, · Legacy Medical Group · Rochester Hills Family Physicians (Corewell) · WellHealth Medical Associates - Rochester · Specialists in Rehabilitation Medicine · University Orthopedic Specialists · Oakland Macomb Surgical Group · Stoney Creek Physicians</t>
         </is>
       </c>
     </row>
@@ -18535,22 +18546,22 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>C-R03</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>C-R19</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Schoenherr Family Practice</t>
+          <t>Kathleen Knapp DO · Brighton Internal Medicine · Byron Medical Group · Howell Family Medicine · Newland Medical Associates - Howell · My Health Urgent Care (Ascension) - Howell · Premier Family Medicine - Livingston · Motor City Ortho - Howell · Advanced Orthopedic Specialists</t>
         </is>
       </c>
     </row>
@@ -18565,39 +18576,39 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>C-R04</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>C-R20</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Faith Internal Medicine &amp; Urgent Care · MEDPRO PRIMARY CARE - Waltz Rd</t>
+          <t>Amro Shata MD · Troy Medical · Somerset Family Medicine - Troy · Family Medicine &amp; Wellness · Premier Private Physicians · Salta Direct Primary Care - Troy · Somerset Pain Clinic · Corewell Health Internal Medicine - Troy · Mathews Medical Center · John Joseph MD,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>C-R06</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>C-R01</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -18606,28 +18617,28 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Office of George Nassif MD</t>
+          <t>Chronic Pain Institute · The Family Doctor · Henry Ford Macomb Internal Medicine · DMC Orthopedics &amp; Sports Medicine - Warren · Office of Steven Trombly MD · Macomb Physicians Group</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>C-R09</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>C-R04+R10+R12+R13</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -18636,33 +18647,33 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Oak Street Health - Eastgate · Oakland Primary Care</t>
+          <t>Cornerstone Internal Medicine · Epic Healthcare - Southfield · Office of Josephine A. Iskander MD · Vital Medicine · GREAT LAKE PHYSICIANS, PC · Oakland Internal Medicine Associates - Henry Ford</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>C-R15</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>C-R05+R06+R07+R09+R11</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Cadence revisit</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
@@ -18670,24 +18681,24 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>ANDERSON SPORTS MEDICINE · Neurology Consultants of Southfield · EPIC Southfield - Telegraph Rd office · Michigan Neurology Associates - Clinton Township · Normandy Family Practice · Michigan MSK Medicine - Clinton Township · Multi-Specialty Clinic · Albert Przybylski DO · Center for Orthopedic Surgery · St Clair Orthpaedics &amp; Sports Medicine - Macomb</t>
+          <t>Preferred Medical Group · Be Well Medical Center · Cornerstone Garfield Family Practice - Ascension · Epic Primary Care - Ferndale · Madison Medical Arts · Barry S Meyer DO PC · Lakeside Internal Medicine · Henry Ford Macomb Health Center - Fraser · Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>C-R16</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>C-R21</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -18696,11 +18707,11 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Corewell Center for Pain Management · Arcturus Healthcare - Rochester Hills · Rochester Medical Group · Phase Family Medicine · Rochester Family Medicine Center · Stamatin Internal Medicine · Rochester Internists · Corewell Internal Medicine Midway · Rochester Family Practice</t>
+          <t>Michigan Internal Medicine &amp; Cardiology Associates · Ortho surgery of shoulder, hip, &amp; knee · Millennium Orthopedics · Tri County Pain Consultants · Healthquest Chiropractic · TRI COUNTY ORTHOPEDICS, PC · McLaren Oakland Center for Spine &amp; Pain Management · Dixie Highway Internal Medicine · Orthopedic Specialists of Oakland County - Clarkston · Independence Urgent Care</t>
         </is>
       </c>
     </row>
@@ -18715,39 +18726,39 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>C-R01</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>C-R22</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Chronic Pain Institute · The Family Doctor · Henry Ford Macomb Internal Medicine · DMC Orthopedics &amp; Sports Medicine - Warren · Office of Steven Trombly MD · Macomb Physicians Group</t>
+          <t>Jolly Neurological Clinic · Poley Sports Medicine · Southeast Michigan Center for Orthopedics - Rochester Hlls · Prism Medical Group - Family Medicine Ste 160 · Prism Medical Group - Family Medicine Ste 240 · Precise Medical · Prism Medical Group - Internal Medicine · Your Physicians · Internal Medicine Associates of Rochester Hills, PC · Physicians in Family Medicine</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>C-R04</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>C-R02+R08+R11</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -18756,28 +18767,28 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Vital Medicine · GREAT LAKE PHYSICIANS, PC</t>
+          <t>Lakeview Medical Center · Gratiot Family Medicine · Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates · Corewell Health Medical Group East · Corewell Health Family Medicine -SAINT CLAIR SHORES · Henry Ford Health Medical Center (Ascension) · Shores Internal Medicine · ESSENTIAL CARE FAMILY MEDICINE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>C-R05</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>C-R12+R13+R14+R15+R16</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -18786,118 +18797,118 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Preferred Medical Group · Be Well Medical Center</t>
+          <t>Belamedica · Hope Medical Center · Precise Chiropractic · Macomb Medical Clinic · EPIC Southfield - Telegraph Rd office · Rochester Medical Group</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>C-R06</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>C-R23</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Cornerstone Garfield Family Practice - Ascension</t>
+          <t>Associated Orthopedists of Detroit-Shelby Township · Alliance - Macomb · Michigan Surgery Specialists - Shelby Township · Alliance - Shelby Township · Shelbydale Medical Clinic PC · MD VIP - Utica · Osteopathic Health Care Associates · PRISM Extended Care and Urgent Care</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>C-R07</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>C-R24</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Epic Primary Care - Ferndale · Madison Medical Arts · Barry S Meyer DO PC</t>
+          <t>Maan Askar MD - Hoover (Thursdays) · Forum Medical Clinic · Julie Henry, MD · Greater Michigan Orthopedics and Sports Medicine - Warren · Midwest Center for Dermatology - Warren · Motor City Orthopedics - Warren · Beaumont Associated Family Care - Warren · Maan Askar MD - 13 Mile</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>C-R09</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>C-R25</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Lakeside Internal Medicine · Henry Ford Macomb Health Center - Fraser</t>
+          <t>Live Well Chiro · Karle Medical Group · Michigan Center For Regenerative Medicine · Ciarlone Orthopedics · Amabir Khaira MD · Meadowbrook Internists · Barclay Internists · Rochester Hills Orthopedics &amp; Sports Medicine · Balanced Living Chiropractic · Colleen Kennedy DO</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>C-R10</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>C-R01+R03+R04+R10+R15+R16+R18+R20</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -18906,28 +18917,28 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>North Valley Internal Medicine</t>
+          <t>Normandy Family Practice · Premier Private Physicians · Faith Internal Medicine &amp; Urgent Care · MEDPRO PRIMARY CARE - Waltz Rd · Corondan Medical · Urgent Care Family · Schoenherr Family Practice · North Valley Internal Medicine · Corewell Internal Medicine Midway · Specialists in Rehabilitation Medicine</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>C-R11</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>C-R05+R06+R07+R09+R14+R17</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -18936,28 +18947,28 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD</t>
+          <t>Premiere Pediatrics · Troy Primary Care · Progressive Health Care · Office of George Nassif MD · John R Medical Clinic · MHP Internal Medicine · Oak Street Health - Eastgate · Oakland Primary Care · Troy Health Center · Saurabh Gupta MD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>C-R12</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>C-R19</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -18966,28 +18977,28 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Cornerstone Internal Medicine · Epic Healthcare - Southfield</t>
+          <t>Brighton Internal Medicine</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>C-R18</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>C-R26</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -18996,58 +19007,58 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Raad Kasmikha MD, · Legacy Medical Group · Rochester Hills Family Physicians (Corewell) · WellHealth Medical Associates - Rochester · Specialists in Rehabilitation Medicine · University Orthopedic Specialists · Oakland Macomb Surgical Group · Stoney Creek Physicians</t>
+          <t>Ruffini DC PC, Richard J · Springfield Urgent Care - Hamburg · Trinity Health System Pain Institute · Associates In Physical Medicine &amp; Rehabilitation · MICHIGAN PAIN SPECIALISTS, PLLC · Michigan Pain Specialists · Clarkston Medical Group Adult &amp; Pediatric Medicine · MOTOR CITY ORTHOPEDICS - Novi · Restorative Physical Medicine - Novi · Urgent Care of Milford</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>C-R02</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>C-R27</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Lakeview Medical Center · Gratiot Family Medicine</t>
+          <t>TRENTON TOTAL HEALTH CARE CENTER, PC · Blanzy Corwell clinic Southgate · MEGHA MOHEY, MD, PC · INTERNAL MEDICINE ASSOCIATES OF MICHIGAN, PC · Corewell Health Taylor Hospital Family Medicine · Great Lakes Health and Wellness · Ghassan Atto PLLC · Family Medicine · Premier Orthopedics</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>C-R08</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>C-R01+R12+R13</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -19056,28 +19067,28 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates</t>
+          <t>Cornerstone Internal Medicine · Epic Healthcare - Southfield · Frederick Karoub MD PC · Office of Josephine A. Iskander MD · Chronic Pain Institute · The Family Doctor · Henry Ford Macomb Internal Medicine · DMC Orthopedics &amp; Sports Medicine - Warren · Office of Steven Trombly MD · Macomb Physicians Group</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>C-R10</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>C-R02+R05+R07+R11</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -19086,28 +19097,28 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Oakland Internal Medicine Associates - Henry Ford</t>
+          <t>Premier Family Physicians · Shaun Jayakar MD · Preferred Medical Group · Be Well Medical Center · Epic Primary Care - Ferndale · Madison Medical Arts · Barry S Meyer DO PC · Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD · Michigan Institute for Neurological Disorders (MIND) - Roseville</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>C-R11</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>C-R21</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -19116,88 +19127,86 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Corewell Health Medical Group East · Corewell Health Family Medicine -SAINT CLAIR SHORES · Henry Ford Health Medical Center (Ascension) · Shores Internal Medicine · ESSENTIAL CARE FAMILY MEDICINE</t>
+          <t>McLaren Oakland Center for Spine &amp; Pain Management</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>C-R12</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>C-R28</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Belamedica</t>
+          <t>Clarkston Internal Medicine · Clarkston Family Medicine · Clarkston Pain &amp; Rehab · Oakland Orthopedics &amp; Sports Medicine · Trinity IHA Primary Care - Clarkston · Clarkston Medical Group · Neuro Pain Consultants - Clarkston · MDVIP Clarkston</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>C-R13</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Office of Josephine A. Iskander MD</t>
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Open slot ×1</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Flex: backlog pull-forward · huddle promotes · ortho field day</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>C-R14</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>C-R02+R06+R08+R09+R14+R15</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -19206,33 +19215,33 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Macomb Medical Clinic</t>
+          <t>Lakeview Medical Center · Gratiot Family Medicine · Cornerstone Garfield Family Practice - Ascension · Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates · Lakeside Internal Medicine · Henry Ford Macomb Health Center - Fraser · Macomb Medical Clinic · EPIC Southfield - Telegraph Rd office</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>C-R19</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>C-R04+R10+R15+R16+R22</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Cadence revisit</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
@@ -19240,967 +19249,35 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Kathleen Knapp DO · Brighton Internal Medicine · Byron Medical Group · Howell Family Medicine · Newland Medical Associates - Howell · My Health Urgent Care (Ascension) - Howell · Premier Family Medicine - Livingston · Motor City Ortho - Howell · Advanced Orthopedic Specialists</t>
+          <t>Neurology Consultants of Southfield · Michigan MSK Medicine - Clinton Township · Vital Medicine · GREAT LAKE PHYSICIANS, PC · Oakland Internal Medicine Associates - Henry Ford · Rochester Medical Group · Prism Medical Group - Family Medicine Ste 240 · Prism Medical Group - Internal Medicine · Physicians in Family Medicine</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>C-R01</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Corondan Medical · Urgent Care Family</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>C-R03</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Schoenherr Family Practice</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>C-R04</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Faith Internal Medicine &amp; Urgent Care · MEDPRO PRIMARY CARE - Waltz Rd</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>C-R05</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Troy Primary Care · Progressive Health Care</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>C-R06</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Office of George Nassif MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>C-R07</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>John R Medical Clinic · MHP Internal Medicine</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>C-R09</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Oak Street Health - Eastgate · Oakland Primary Care</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>C-R13</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Hope Medical Center · Precise Chiropractic</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>C-R14</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Troy Health Center · Saurabh Gupta MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>C-R15</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>EPIC Southfield - Telegraph Rd office</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>C-R16</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Rochester Medical Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>C-R17</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Premiere Pediatrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>C-R21</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>McLaren Oakland Center for Spine &amp; Pain Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>C-R01</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Chronic Pain Institute · The Family Doctor · Henry Ford Macomb Internal Medicine · DMC Orthopedics &amp; Sports Medicine - Warren · Office of Steven Trombly MD · Macomb Physicians Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>C-R02</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Premier Family Physicians · Shaun Jayakar MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>C-R05</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Preferred Medical Group · Be Well Medical Center</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>C-R07</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Epic Primary Care - Ferndale · Madison Medical Arts · Barry S Meyer DO PC</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>C-R10</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>North Valley Internal Medicine</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>C-R11</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Henry Ford St. John Center for Wellness · Michigan Institute for Neurological Disorders (MIND) - Roseville · Sudha Nannapaneni MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>C-R12</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Cornerstone Internal Medicine · Frederick Karoub MD PC · Epic Healthcare - Southfield</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>C-R15</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Normandy Family Practice</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>C-R16</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>Corewell Internal Medicine Midway</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>C-R18</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>Specialists in Rehabilitation Medicine</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>C-R02</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Lakeview Medical Center · Gratiot Family Medicine</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>C-R04</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Vital Medicine · GREAT LAKE PHYSICIANS, PC</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>C-R06</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Cornerstone Garfield Family Practice - Ascension</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>C-R08</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>C-R09</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>Lakeside Internal Medicine · Henry Ford Macomb Health Center - Fraser</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>C-R13</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Office of Josephine A. Iskander MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>C-R14</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Macomb Medical Clinic</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>C-R19</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Brighton Internal Medicine</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>C-R20</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>Amro Shata MD · Troy Medical · Somerset Family Medicine - Troy · Family Medicine &amp; Wellness · Premier Private Physicians · Salta Direct Primary Care - Troy · Somerset Pain Clinic · Corewell Health Internal Medicine - Troy · Mathews Medical Center · John Joseph MD,</t>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Open slot ×3</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>Flex: backlog pull-forward · huddle promotes · ortho field day</t>
         </is>
       </c>
     </row>
@@ -20275,2193 +19352,2193 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>96903a48-13a7-42e0-8f5e-a56cce365ea5</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Anchor Bay Clinic Family Medical Center</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>New Baltimore</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Now HF affiliated</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>b9b7ff1f-a14b-4733-af73-e7371152c69a</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Macomb Family Medicine (Henry Ford) - Chesterfield</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Chesterfield</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr"/>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr"/>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>1619909793</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Dennis G Kelly DO</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Madison Heights</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr"/>
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>1023116068</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Center for Preventative Medicine</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Grosse Pointe</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr"/>
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>7e174398-087f-41d2-8f79-7c1a94c070e5</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Henry Ford Macomb Orthopedic Surgery - Washington</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Washington</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>66604f44-0a10-4e2a-8f1e-c4e00f0fb1dc</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Partners in Family Medicine</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Shelby Township</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>da7a2e70-7373-4808-9950-99c98f41d55e</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Blue Water Pain Specialists - Macomb</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Macomb</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>e33f4068-dcba-4ec6-a5b6-a0ce07fd66d3</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Michigan Head &amp; Spine Institute - Macomb</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Clinton Township</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>aaaaf0e6-b931-49ae-be22-319368bfc366</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>IHA Hand Surgery - Brighton</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>BRIGHTON</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>6abec30d-30ef-4f35-8e04-85112389bfb1</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>JOEL WELLNESS CLINIC</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Livonia</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr"/>
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>a320a856-33fb-458b-8907-d98101fceb1b</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Roger D Ajluni MD PC</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Livonia</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr"/>
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>7ba5f22d-a044-4e77-9eae-086d15413f50</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Beacon Orthopedics of Michigan - Livonia</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Livonia</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr"/>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>80d59d4a-83b2-4eff-a6a5-58214e7bf1ba</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Blue Water Pain Specialists - St Clair Shores</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>St. Clair Shores</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr"/>
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>96920148-57be-4764-88fe-0131ee3733e7</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Arora Hand Surgery - Warren</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Warren</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr"/>
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>1538237060</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Henry Ford Medical Center - Beck Rd</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Plymouth</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr"/>
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>1fcb9ed3-4f7b-4998-b644-3c8f0d4fefba</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>UofM Northville Health Center</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Northville</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr"/>
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>1972528818</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Levan Internists</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Livonia</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Not my account. Being called on by Jasmine</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Reassigned to Jasmine’s routes — pending Kristen confirmation</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>af12dee4-a837-45cd-b77e-ae4d5a1da5b3</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Primary Care Services -Westland</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Westland</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr"/>
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>844e3cfa-90dd-4405-b93e-8ec8a51a6b23</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>MSU SportsMEDICINE</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>East Lansing</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr"/>
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>20a601f2-ef2f-40db-b5ec-481cf50305de</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Henry Ford Internal Medicine - Sterling Heights</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Sterling Heights</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr"/>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>c47f040d-217f-4526-bd80-92b1073a4d77</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Foot &amp; Ankle Specialists of Southeast Michigan - Warren</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Other / Verify</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Warren</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr"/>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>1609867985</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Beaumont Neurosurgery</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Troy</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr"/>
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>5bb9aa8b-846a-4a0b-ab77-289399d9b1b1</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Glowacki MD - Institute for Pain, Spine &amp; Headache Disorders</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Troy</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr"/>
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>c796443f-9c0a-4e5d-9f5a-df76d3e311bc</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Ascension Providence Partners in Womens Health</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Southfield</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr"/>
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>2fc64685-2270-4f5f-827a-7788409cd5cd</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Pulmonary &amp; Internal Medicine Specialists</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Southfield</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr"/>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr"/>
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>15d2de97-a164-4b7e-a3a2-15673271319b</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Specialists in Spine Surgery - Garden City</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Garden City</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr"/>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr"/>
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>0c7e4fda-32b4-4999-afc5-3ead3985f8c9</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Michigan Orthopaedic &amp; Spine Surgeons</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr"/>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr"/>
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>d606572a-912c-4bad-b906-c9a8d0479eff</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Clarkston Medical Group - Oxford</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>OXFORD</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr"/>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr"/>
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>172f7e80-1532-4f45-8c82-d3d09547c86d</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>David S Hollett MD</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr"/>
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>118d4718-8c24-42b0-ae12-a1975f146750</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Henry Ford Macomb Orthopedics - Chesterfield</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Chesterfield</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr"/>
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>1275554073</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Chesterfield Family Medicine (Henry Ford)</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>New Baltimore</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr"/>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>d361f230-715e-4c7e-87a9-bf50246f42f4</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Eastside Neurosurgery - Macomb</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Macomb</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr"/>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr"/>
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>a2352347-063f-4a39-a0c1-25774fd3490b</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Michigan Head &amp; Spine Institute - Novi</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Novi</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr"/>
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>1244d3ff-0839-4759-af42-e22dd1c77549</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Niva Health</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Novi</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr"/>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr"/>
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>989f0eea-dc08-4445-9a51-ee7663255964</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Michigan Spine Institute</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Waterford Township</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr"/>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr"/>
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>d52215b9-d874-4639-9ff2-a87b853ad52d</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Adult Wellness &amp; Internal Medicine</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Flint</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr"/>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr"/>
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>4dd7647d-ac5e-4f26-a696-b59cd2cfb219</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Mid-Michigan Pain Specialty</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Flint</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr"/>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr"/>
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>1235110537</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Ortho Michigan - Flint</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Flint</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr"/>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr"/>
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>74360f7a-f042-4521-a7bb-a807dcb10282</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>Advance Urgent Care - Hartland</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Urgent Care</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Hartland</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr"/>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr"/>
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>a29bc662-1f09-48ea-a1f5-efe24cc01eeb</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Great Lakes Medicine</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>ER / Hospital</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Shelby Twp</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr"/>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr"/>
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>3bfd16c2-8d66-4fed-9ad2-cc715dfd2eb8</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>Revolution Wellness</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Utica</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr"/>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr"/>
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>4d38264b-b17e-42b4-9043-92ff06e62c09</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>WARREN PODIATRY</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>Other / Verify</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>WARREN</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr"/>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr"/>
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>c2e9f4c4-65ff-4730-abe0-7f210be0bf8f</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>Michigan Brain &amp; Spine - Warren</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Warren</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr"/>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr"/>
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>9b6db0bd-31b4-4d7e-b351-e4ee78a4defa</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>Trinity IHA Primary Care - Rochester Hills</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr"/>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr"/>
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>7c9505b8-9a32-47d6-a489-6171ce848c9e</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>LMT Rehabilitation Associates - Troy</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Troy</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr"/>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr"/>
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>c48a8a2e-4d60-4a18-8000-3f3dea9cf03a</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>DEVYANI KHAMBETE, MD, PC</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>WATERFORD</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr"/>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr"/>
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>ff09ce61-5da4-4d5d-9ae6-7b9215731ce9</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>McLaren Center for Spine &amp; Pain Management</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Clinton Township</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr"/>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr"/>
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>4d131d76-2f91-472e-bf42-c1ae3f5f7622</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>McLaren Macomb Family First</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Clinton Township</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr"/>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr"/>
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>f5b10e96-2444-4c72-b938-1004495c7ee3</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>Ernest Chiodo MD</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>CLINTON TOWNSHIP</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr"/>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr"/>
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>54898915-220c-4900-ba07-febdcdb005c0</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>Edward A. Tashjian, MD - Clarkston</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>City of the Village of Clarkston</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr"/>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr"/>
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>e0f2c54e-06ee-4e34-863e-cb4675bd5c6e</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>PINE TREE MEDICAL CENTER</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>WATERFORD</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr"/>
-      <c r="G53" s="10" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr"/>
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>c3b6301b-b3bc-474d-9ddd-d21fd2c40797</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>Health First Medical Center</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>SOUTHGATE</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr"/>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr"/>
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>aaded854-5fe8-4282-b99d-3af289b977e0</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>Back &amp; Pain Center (UofM) at Burlington Bldg</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
         <is>
           <t>Ann Arbor</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr"/>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="F55" s="12" t="inlineStr"/>
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>4430ce9a-04c4-4489-8cd4-1f4abdc28ce9</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>U of M Physical Medicine &amp; Rehabilitation Clinic - Burlington Building</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>Ann Arbor</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr"/>
-      <c r="G56" s="10" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr"/>
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>c357306a-7118-459d-82fc-5365721ca926</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>U of M Neurosurgery</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E57" s="11" t="inlineStr">
         <is>
           <t>Ann Arbor</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr"/>
-      <c r="G57" s="10" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr"/>
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>6900d9f0-9d28-423a-98a4-281fb9ac13c1</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>IHA Ann Arbor Orthpaedic Specialists</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>Ypsilanti</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr"/>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr"/>
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>b6be5dd0-40a2-450c-946b-5deaaf8b0178</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>Trinity IHA Hand Surgery - Ypsilanti</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E59" s="11" t="inlineStr">
         <is>
           <t>Ypsilanti</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr"/>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr"/>
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>19d50314-6b7d-4516-94cb-e3c191c3fde1</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>MedSport - Ann Arbor Domino's Farms</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="E60" s="11" t="inlineStr">
         <is>
           <t>Ann Arbor</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr"/>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr"/>
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>42caeada-e3af-49fd-ab98-cc39cf1a5ffe</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>Chelsea Physical Medicine &amp; Rehabilitation Specialists</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E61" s="11" t="inlineStr">
         <is>
           <t>Chelsea</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr"/>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr"/>
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>1033228903</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>Trinity Health IHA Orthopaedics - Chelsea</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E62" s="11" t="inlineStr">
         <is>
           <t>Chelsea</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr"/>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr"/>
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>e73e7e8b-2c72-479d-b015-c7ff5509f700</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>Precision Interventional Radiology</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t>FARMINGTON HILLS</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr"/>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="F63" s="12" t="inlineStr"/>
+      <c r="G63" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>2b5bba73-5878-4fa6-b615-7b5106bbe4e0</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>SPINE SPECIALISTS OF MICHIGAN, PC</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E64" s="11" t="inlineStr">
         <is>
           <t>BINGHAM FARMS</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr"/>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="F64" s="12" t="inlineStr"/>
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>1619959566</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>Beaumont Royal Oak - Physical Medicine &amp; Rehabilitation</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E65" s="11" t="inlineStr">
         <is>
           <t>Royal Oak</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr"/>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr"/>
+      <c r="G65" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>4c1b7fe8-a5c4-417f-bee6-92fae75a3c35</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>Spine &amp; Brain Surgery Specialists</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="E66" s="11" t="inlineStr">
         <is>
           <t>Royal Oak</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr"/>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="F66" s="12" t="inlineStr"/>
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>d012f6c8-f44d-46a5-9f8e-b3b522de7d83</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Arthritis Physicians</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr"/>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="F67" s="12" t="inlineStr"/>
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>47bcf8c4-c5dc-4d5a-9a9e-4bece6e01698</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>Premier Surgical Specialists</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr"/>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr"/>
+      <c r="G68" s="12" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>Your 82 “Not sure” rows stay in the routes (amber in Stops tab) and go to the Jul 31 consolidation with Joel — they are NOT removed.</t>
         </is>

--- a/pm/route-days-v2/Spine-Route-Days-Coty.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Coty.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coty — Spine Route Days v2 · validated universe (your eyeball pass, Jul 31) · “No” accounts removed · cadence: T1 21d · T2 30d · T3/prospect 45d</t>
+          <t>Coty — Spine Route Days v2 · validated universe (eyeball pass, Jul 31) · “No” accounts removed · cadence: T1 21d · T2 30d · T3/prospect 45d</t>
         </is>
       </c>
     </row>

--- a/pm/route-days-v2/Spine-Route-Days-Coty.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Coty.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,11 +45,6 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="10"/>
     </font>
     <font>
       <i val="1"/>
@@ -101,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -125,11 +120,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -137,7 +129,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coty — Spine Route Days v2 · validated universe (eyeball pass, Jul 31) · “No” accounts removed · cadence: T1 21d · T2 30d · T3/prospect 45d</t>
+          <t>Coty — HOME ROUTE DAYS (your territory reference, 28 days). These are the geographic clusters your accounts belong to — the days you actually drive are on the Weekly Plan tab. Validated universe (eyeball pass, Jul 31); cadence T1 21d · T2 30d · T3/prospect 45d.</t>
         </is>
       </c>
     </row>
@@ -619,7 +611,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -664,7 +656,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -799,7 +791,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -889,7 +881,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -934,7 +926,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1114,7 +1106,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1204,7 +1196,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1294,7 +1286,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1339,7 +1331,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1384,7 +1376,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1429,7 +1421,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1474,7 +1466,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1519,7 +1511,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1564,7 +1556,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1609,7 +1601,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -1654,7 +1646,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -1699,7 +1691,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -1744,7 +1736,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -1789,7 +1781,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -1834,7 +1826,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -17945,21 +17937,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="68" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5 route-day slots per week. First pass = the full day. Cadence revisit = the producers due on rhythm, packed into one full loop day (a label like R03+R07 = one drive covering both days’ producers). Open slots are flex. Pick weekdays at the Monday huddle.</t>
+          <t>ONE ROW = ONE DAY YOU DRIVE. Day K-W1D1 means week 1, day 1 — the Stops column is the whole day, nothing to add up. Each day is built from whoever is due that week in one area (Tier 1 every 21 days · Tier 2 30 · Tier 3 45), with prospects from the same area riding along to fill it. “From home days” points back to the Route Days tab. Pick the weekday at the Monday huddle.</t>
         </is>
       </c>
     </row>
@@ -17976,172 +17974,312 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Route Day(s)</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Visit Kind</t>
+          <t>Stops</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Stops</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Who you’ll see</t>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Prospects</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Primary Area</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>From home days</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Navigate</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Who you’ll see (in order)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>C-R03</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Gregory Gould DO · Alliance Washington Township · Washington Family Medicine · Neuro Pain Consultants - Shelby · Get Well Urgent Care of Shelby · Stonebridge Orthopedics · Schoenherr Family Practice · Macomb Family Medical Center</t>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>C-W1D1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Clinton Township (4) • Macomb (3) • Troy (1)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>R06, R12</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Cornerstone Garfield Family Practice - Ascension · Orthopedic Surgery of Macomb · Movement Orthopedics · Keystone Partners - Macomb · Woods Cardiovascular Internal Medicine Associates - Macomb · Cornerstone Internal Medicine · Belamedica · Neuro Pain Consultants - Sterling Heights · Cheryl Lerchin MD Physical Medicine &amp; Rehabilitation · Office of George Nassif MD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>C-R04</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>C-W1D2</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>GREAT LAKES ORTHOPAEDICS · Vital Medicine · Rosemary Aquiler-Angeles MD · Enhance Center - Livonia · GREAT LAKE PHYSICIANS, PC · Michigan Physicians Group - Livonia · Faith Internal Medicine &amp; Urgent Care · MEDPRO PRIMARY CARE - Waltz Rd · Downriver Internists - Wayne · MDWELL -CO</t>
+      <c r="E4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Warren (5) • St. Clair Shores (2) • Clinton Township (1)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>R09, R24</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Midwest Center for Dermatology - Warren · Beaumont Associated Family Care - Warren · Henry Ford Macomb Health Center - Fraser · Oak Street Health - Eastgate · Lakeside Internal Medicine · George Afram MD, · Maridel Hernadez MD · Oakland Primary Care · Metro Pain Clinic  - Warren · Center For Physical Medicine &amp; Rehabilitation - Warren</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>C-R06</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Keystone Partners - Macomb · Woods Cardiovascular Internal Medicine Associates - Macomb · Cornerstone Garfield Family Practice - Ascension · Office of George Nassif MD · Orthopedic Surgery of Macomb · Movement Orthopedics · Neuro Pain Consultants - Sterling Heights · Cheryl Lerchin MD Physical Medicine &amp; Rehabilitation</t>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>C-W1D3</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Shelby Township (6) • Washington (2) • Macomb (1)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>R03, R23</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Macomb Family Medical Center · Gregory Gould DO · Alliance Washington Township · Associated Orthopedists of Detroit-Shelby Township · Alliance - Macomb · Get Well Urgent Care of Shelby · Stonebridge Orthopedics · Schoenherr Family Practice · Neuro Pain Consultants - Shelby · Washington Family Medicine</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>C-R09</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Maridel Hernadez MD · George Afram MD, · Lakeside Internal Medicine · Oak Street Health - Eastgate · Oakland Primary Care · Metro Pain Clinic  - Warren · Center For Physical Medicine &amp; Rehabilitation - Warren · Henry Ford Macomb Health Center - Fraser</t>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>C-W1D4</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Brighton (4) • Milford (2) • Milford Charter Township (2)</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>R10, R26</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Trinity IHA Orthopedics - Brighton, · Core Institute - Brighton · Restorative Physical Medicine - Brighton · Lederman Kwartowitz - Brighton · Clarkston Medical Group Adult &amp; Pediatric Medicine · North Valley Internal Medicine · Providence Family &amp; Athletic Medicine · Oakland Internal Medicine Associates - Henry Ford · Prime Internal Medicine (MDVIP) · DMC Primary and Specialty Care - Milford</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>C-R10</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Trinity IHA Orthopedics - Brighton, · Core Institute - Brighton · Restorative Physical Medicine - Brighton · Lederman Kwartowitz - Brighton · Providence Family &amp; Athletic Medicine · Oakland Internal Medicine Associates - Henry Ford · Prime Internal Medicine (MDVIP) · DMC Primary and Specialty Care - Milford · North Valley Internal Medicine</t>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C-W1D5</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Livonia (6) • Troy (2) • City Of The Village Of Clarkston (1)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>R04, R17</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Premiere Pediatrics · Michigan Institute for Neurological Disorders (MIND) - Farmington Hills · Jagannathan Neurosurgery · CarePoint Internal Medicine · Vital Medicine · Rosemary Aquiler-Angeles MD · Enhance Center - Livonia · GREAT LAKE PHYSICIANS, PC · Michigan Physicians Group - Livonia · Faith Internal Medicine &amp; Urgent Care</t>
         </is>
       </c>
     </row>
@@ -18156,22 +18294,44 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>C-R01</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>C-W2D1</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Chronic Pain Institute · The Family Doctor · Henry Ford Macomb Internal Medicine · DMC Orthopedics &amp; Sports Medicine - Warren · Office of Steven Trombly MD · Macomb Physicians Group</t>
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Roseville (5) • Saint Clair Shores (3) • St. Clair Shores (2)</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Corewell Health Family Medicine -SAINT CLAIR SHORES · ESSENTIAL CARE FAMILY MEDICINE · Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD · Corewell Health Medical Group East · Michigan Surgery Specialists  - Roseville · Michigan Institute for Neurological Disorders (MIND) - Roseville · Shores Internal Medicine · Henry Ford Health Medical Center (Ascension) · Premier Orthopedics &amp; Sports Medicine</t>
         </is>
       </c>
     </row>
@@ -18186,22 +18346,44 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>C-R05+R07</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>C-W2D2</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Preferred Medical Group · Be Well Medical Center · Epic Primary Care - Ferndale · Madison Medical Arts · Barry S Meyer DO PC</t>
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Troy (4) • Madison Heights (3) • Sterling Heights (2)</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>R14, R20</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Saurabh Gupta MD · Mi Family Medicine &amp; Urgent Care · Oakland Macomb Surgical Group - Madison Heights · Troy Health Center · Detroit Ortho Institute · Premier Private Physicians · Somerset Pain Clinic · Farrah Ahmad MD · Macomb Medical Clinic · AS Medical Group</t>
         </is>
       </c>
     </row>
@@ -18216,22 +18398,44 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>C-R11</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>C-W2D3</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD · Corewell Health Medical Group East · Michigan Surgery Specialists  - Roseville · Michigan Institute for Neurological Disorders (MIND) - Roseville · Corewell Health Family Medicine -SAINT CLAIR SHORES · Premier Orthopedics &amp; Sports Medicine · Henry Ford Health Medical Center (Ascension) · Shores Internal Medicine · ESSENTIAL CARE FAMILY MEDICINE</t>
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Howell (8) • Brighton (1)</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Orthopedic Specialists · Kathleen Knapp DO · Brighton Internal Medicine · Byron Medical Group · Howell Family Medicine · Newland Medical Associates - Howell · My Health Urgent Care (Ascension) - Howell · Premier Family Medicine - Livingston · Motor City Ortho - Howell</t>
         </is>
       </c>
     </row>
@@ -18246,22 +18450,44 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>C-R12</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>C-W2D4</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Emil Sitto MD · McLaren Macomb Primary Care · Romeo Plank Family Practice · Cornerstone Internal Medicine · Silver Pine Medical Group Romeo Plank · Neuro Pain Consultants - Macomb · Frederick Karoub MD PC · Epic Healthcare - Southfield · Medpointe urgent care - St Clair Shores · Belamedica</t>
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Troy (4) • Sterling Heights (4) • Hartland (1)</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>R13, R17</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>HARTLAND PEDIATRICS · Regenerative Pain Medicine · MDVIP - Troy · Changee Kim MD · Precise Chiropractic · Bones &amp; Joints Clinic · Hope Medical Center · Office of Josephine A. Iskander MD · Forum Medical Clinic · Greater Michigan Orthopedics</t>
         </is>
       </c>
     </row>
@@ -18276,172 +18502,304 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>C-R13</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>C-W2D5</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Rochester Hills (8) • Troy (1) • Rochester (1)</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>R16, R18</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Phase Family Medicine · Specialists in Rehabilitation Medicine · Corewell Center for Pain Management · Arcturus Healthcare - Rochester Hills · Rochester Medical Group · Rochester Family Medicine Center · Stamatin Internal Medicine · Rochester Internists · Corewell Internal Medicine Midway · Rochester Family Practice</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C-W3D1</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Regenerative Pain Medicine · MDVIP - Troy · Bones &amp; Joints Clinic · Hope Medical Center · Changee Kim MD · Precise Chiropractic · Office of Josephine A. Iskander MD · Forum Medical Clinic</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Farmington Hills (3) • City Of The Village Of Clarkston (3) • Clarkston (2)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>R21, R28</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Michigan Internal Medicine &amp; Cardiology Associates · Ortho surgery of shoulder, hip, &amp; knee · Millennium Orthopedics · Tri County Pain Consultants · Healthquest Chiropractic · McLaren Oakland Center for Spine &amp; Pain Management · Dixie Highway Internal Medicine · Orthopedic Specialists of Oakland County - Clarkston · Clarkston Medical Group · Independence Urgent Care</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>C-R01</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C-W3D2</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Rochester Hills (9) • Bloomfield Township (1)</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Jolly Neurological Clinic · Poley Sports Medicine · Southeast Michigan Center for Orthopedics - Rochester Hlls · Prism Medical Group - Family Medicine Ste 160 · Prism Medical Group - Family Medicine Ste 240 · Precise Medical · Prism Medical Group - Internal Medicine · Your Physicians · Internal Medicine Associates of Rochester Hills, PC · Physicians in Family Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C-W3D3</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Corondan Medical · Urgent Care Family</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="G15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Rochester Hills (7) • Rochester (3)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Michigan Center For Regenerative Medicine · Barclay Internists · Colleen Kennedy DO · Live Well Chiro · Karle Medical Group · Ciarlone Orthopedics · Amabir Khaira MD · Meadowbrook Internists · Rochester Hills Orthopedics &amp; Sports Medicine · Balanced Living Chiropractic</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>C-R02+R05+R07+R08</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Lakeview Medical Center · Gratiot Family Medicine · Troy Primary Care · Progressive Health Care · John R Medical Clinic · MHP Internal Medicine · Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C-W3D4</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Clinton Township (6) • Bingham Farms (1) • Southfield (1)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>R12, R15</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>ANDERSON SPORTS MEDICINE · EPIC Southfield - Telegraph Rd office · Michigan Neurology Associates - Clinton Township · Normandy Family Practice · Michigan MSK Medicine - Clinton Township · Multi-Specialty Clinic · Albert Przybylski DO · Center for Orthopedic Surgery · St Clair Orthpaedics &amp; Sports Medicine - Macomb · Frederick Karoub MD PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>C-R14</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C-W3D5</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Troy Health Center · Detroit Ortho Institute · Macomb Medical Clinic · Farrah Ahmad MD · AS Medical Group · Mi Family Medicine &amp; Urgent Care · Oakland Macomb Surgical Group - Madison Heights · Saurabh Gupta MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>C-R15</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>ANDERSON SPORTS MEDICINE · Neurology Consultants of Southfield · EPIC Southfield - Telegraph Rd office · Michigan Neurology Associates - Clinton Township · Normandy Family Practice · Michigan MSK Medicine - Clinton Township · Multi-Specialty Clinic · Albert Przybylski DO · Center for Orthopedic Surgery · St Clair Orthpaedics &amp; Sports Medicine - Macomb</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>C-R16</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Corewell Center for Pain Management · Arcturus Healthcare - Rochester Hills · Rochester Medical Group · Phase Family Medicine · Rochester Family Medicine Center · Stamatin Internal Medicine · Rochester Internists · Corewell Internal Medicine Midway · Rochester Family Practice</t>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Southgate (5) • Allen Park (1) • Dearborn (1)</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>R26, R27</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Family Medicine · Premier Orthopedics · Great Lakes Health and Wellness · TRENTON TOTAL HEALTH CARE CENTER, PC · Springfield Urgent Care - Hamburg · MEGHA MOHEY, MD, PC · INTERNAL MEDICINE ASSOCIATES OF MICHIGAN, PC · Blanzy Corwell clinic Southgate · Corewell Health Taylor Hospital Family Medicine · Ghassan Atto PLLC</t>
         </is>
       </c>
     </row>
@@ -18456,22 +18814,44 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>C-R02+R03+R04+R06+R09+R10</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>C-W4D1</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Premier Family Physicians · Shaun Jayakar MD · Office of George Nassif MD · Oak Street Health - Eastgate · Oakland Primary Care · Faith Internal Medicine &amp; Urgent Care · MEDPRO PRIMARY CARE - Waltz Rd · Schoenherr Family Practice · North Valley Internal Medicine</t>
+        <v>4</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Macomb (6) • Southfield (1) • St. Clair Shores (1)</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>R06, R09, R12</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Emil Sitto MD · McLaren Macomb Primary Care · Romeo Plank Family Practice · Cornerstone Internal Medicine · Silver Pine Medical Group Romeo Plank · Neuro Pain Consultants - Macomb · Epic Healthcare - Southfield · Medpointe urgent care - St Clair Shores · Oakland Primary Care · Office of George Nassif MD</t>
         </is>
       </c>
     </row>
@@ -18486,22 +18866,44 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>C-R17</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>C-W4D2</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Premiere Pediatrics · HARTLAND PEDIATRICS · Michigan Institute for Neurological Disorders (MIND) - Farmington Hills · Jagannathan Neurosurgery · CarePoint Internal Medicine · AMG Oak Park Medical Center · Greater Michigan Orthopedics · Flint Children’s Center</t>
+        <v>5</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Madison Heights (4) • Berkley (2) • Troy (2)</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>R05, R07, R20</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Preferred Medical Group · John R Medical Clinic · Madison Medical Arts · MHP Internal Medicine · Progressive Health Care · Be Well Medical Center · Mathews Medical Center · Troy Primary Care · Barry S Meyer DO PC · Epic Primary Care - Ferndale</t>
         </is>
       </c>
     </row>
@@ -18516,22 +18918,44 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>C-R18</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>C-W4D3</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Raad Kasmikha MD, · Legacy Medical Group · Rochester Hills Family Physicians (Corewell) · WellHealth Medical Associates - Rochester · Specialists in Rehabilitation Medicine · University Orthopedic Specialists · Oakland Macomb Surgical Group · Stoney Creek Physicians</t>
+        <v>6</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Sterling Heights (5) • Warren (3) • Clinton Township (1)</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>R01, R24</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>The Family Doctor · Julie Henry, MD · Corondan Medical · Forum Medical Clinic · Office of Steven Trombly MD · Urgent Care Family · Henry Ford Macomb Internal Medicine · Macomb Physicians Group · DMC Orthopedics &amp; Sports Medicine - Warren · Chronic Pain Institute</t>
         </is>
       </c>
     </row>
@@ -18546,22 +18970,44 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>C-R19</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>C-W4D4</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Kathleen Knapp DO · Brighton Internal Medicine · Byron Medical Group · Howell Family Medicine · Newland Medical Associates - Howell · My Health Urgent Care (Ascension) - Howell · Premier Family Medicine - Livingston · Motor City Ortho - Howell · Advanced Orthopedic Specialists</t>
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Troy (5) • Roseville (1) • Saint Clair Shores (1)</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>R02, R09, R20</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Oak Street Health - Eastgate · Premier Family Physicians · Shaun Jayakar MD · Lakeview Medical Center · John Joseph MD, · Troy Medical · Somerset Family Medicine - Troy · Salta Direct Primary Care - Troy · Corewell Health Internal Medicine - Troy · Gratiot Family Medicine</t>
         </is>
       </c>
     </row>
@@ -18576,172 +19022,304 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>C-R20</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>C-W4D5</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Warren (2) • Novi (2) • City Of The Village Of Clarkston (1)</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>R04, R17, R24, R26</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Premiere Pediatrics · Greater Michigan Orthopedics and Sports Medicine - Warren · Maan Askar MD - 13 Mile · Faith Internal Medicine &amp; Urgent Care · MEDPRO PRIMARY CARE - Waltz Rd · Trinity Health System Pain Institute · MOTOR CITY ORTHOPEDICS - Novi · Restorative Physical Medicine - Novi · Urgent Care of Milford · Flint Children’s Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C-W5D1</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Roseville (2) • Clinton Township (1) • New Baltimore (1)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>R06, R08, R11, R12</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Cornerstone Garfield Family Practice - Ascension · Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates · Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD · Belamedica</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C-W5D2</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Amro Shata MD · Troy Medical · Somerset Family Medicine - Troy · Family Medicine &amp; Wellness · Premier Private Physicians · Salta Direct Primary Care - Troy · Somerset Pain Clinic · Corewell Health Internal Medicine - Troy · Mathews Medical Center · John Joseph MD,</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="E24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Shelby Township (6) • Rochester Hills (2) • Shebly Township (1)</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>R03, R16, R23</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Rochester Medical Group · PRISM Extended Care and Urgent Care · Associated Orthopedists of Detroit-Shelby Township · Alliance - Macomb · Michigan Surgery Specialists - Shelby Township · Schoenherr Family Practice · MD VIP - Utica · Alliance - Shelby Township · Shelbydale Medical Clinic PC · Osteopathic Health Care Associates</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>C-R01</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C-W5D3</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Chronic Pain Institute · The Family Doctor · Henry Ford Macomb Internal Medicine · DMC Orthopedics &amp; Sports Medicine - Warren · Office of Steven Trombly MD · Macomb Physicians Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Clarkston (4) • City Of The Village Of Clarkston (2) • Village Of Clarkston (1)</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>R10, R19, R26, R28</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Oakland Orthopedics &amp; Sports Medicine · Clarkston Family Medicine · Neuro Pain Consultants - Clarkston · Clarkston Internal Medicine · Trinity IHA Primary Care - Clarkston · MDVIP Clarkston · Clarkston Medical Group Adult &amp; Pediatric Medicine · North Valley Internal Medicine · Oakland Internal Medicine Associates - Henry Ford · Brighton Internal Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>C-R04+R10+R12+R13</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Cornerstone Internal Medicine · Epic Healthcare - Southfield · Office of Josephine A. Iskander MD · Vital Medicine · GREAT LAKE PHYSICIANS, PC · Oakland Internal Medicine Associates - Henry Ford</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C-W5D4</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Warren (3) • Troy (3) • Sterling Heights (2)</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>R09, R13, R14, R20, R24</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Midwest Center for Dermatology - Warren · Beaumont Associated Family Care - Warren · Henry Ford Macomb Health Center - Fraser · Lakeside Internal Medicine · Amro Shata MD · Family Medicine &amp; Wellness · Premier Private Physicians · Maan Askar MD - Hoover (Thursdays) · Macomb Medical Clinic · Office of Josephine A. Iskander MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>C-R05+R06+R07+R09+R11</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Preferred Medical Group · Be Well Medical Center · Cornerstone Garfield Family Practice - Ascension · Epic Primary Care - Ferndale · Madison Medical Arts · Barry S Meyer DO PC · Lakeside Internal Medicine · Henry Ford Macomb Health Center - Fraser · Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>C-R21</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Michigan Internal Medicine &amp; Cardiology Associates · Ortho surgery of shoulder, hip, &amp; knee · Millennium Orthopedics · Tri County Pain Consultants · Healthquest Chiropractic · TRI COUNTY ORTHOPEDICS, PC · McLaren Oakland Center for Spine &amp; Pain Management · Dixie Highway Internal Medicine · Orthopedic Specialists of Oakland County - Clarkston · Independence Urgent Care</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>C-R22</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Jolly Neurological Clinic · Poley Sports Medicine · Southeast Michigan Center for Orthopedics - Rochester Hlls · Prism Medical Group - Family Medicine Ste 160 · Prism Medical Group - Family Medicine Ste 240 · Precise Medical · Prism Medical Group - Internal Medicine · Your Physicians · Internal Medicine Associates of Rochester Hills, PC · Physicians in Family Medicine</t>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C-W5D5</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Rochester (4) • Rochester Hills (4)</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Rochester Hills Family Physicians (Corewell) · WellHealth Medical Associates - Rochester · Specialists in Rehabilitation Medicine · University Orthopedic Specialists · Oakland Macomb Surgical Group · Stoney Creek Physicians · Legacy Medical Group · Raad Kasmikha MD,</t>
         </is>
       </c>
     </row>
@@ -18756,22 +19334,44 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>C-R02+R08+R11</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>C-W6D1</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Lakeview Medical Center · Gratiot Family Medicine · Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates · Corewell Health Medical Group East · Corewell Health Family Medicine -SAINT CLAIR SHORES · Henry Ford Health Medical Center (Ascension) · Shores Internal Medicine · ESSENTIAL CARE FAMILY MEDICINE</t>
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Saint Clair Shores (3) • Southfield (2) • Madison Heights (1)</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>R11, R14, R15, R24</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Corewell Health Family Medicine -SAINT CLAIR SHORES · ESSENTIAL CARE FAMILY MEDICINE · Saurabh Gupta MD · Neurology Consultants of Southfield · EPIC Southfield - Telegraph Rd office · Corewell Health Medical Group East · Shores Internal Medicine · Henry Ford Health Medical Center (Ascension) · Troy Health Center · Motor City Orthopedics - Warren</t>
         </is>
       </c>
     </row>
@@ -18786,505 +19386,504 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>C-R12+R13+R14+R15+R16</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>C-W6D2</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Belamedica · Hope Medical Center · Precise Chiropractic · Macomb Medical Clinic · EPIC Southfield - Telegraph Rd office · Rochester Medical Group</t>
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Livonia (2) • City Of The Village Of Clarkston (2) • Troy (1)</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>R04, R13, R16, R21, R28</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Precise Chiropractic · Vital Medicine · GREAT LAKE PHYSICIANS, PC · Corewell Internal Medicine Midway · Hope Medical Center · Clarkston Pain &amp; Rehab · McLaren Oakland Center for Spine &amp; Pain Management</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>C-R23</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Associated Orthopedists of Detroit-Shelby Township · Alliance - Macomb · Michigan Surgery Specialists - Shelby Township · Alliance - Shelby Township · Shelbydale Medical Clinic PC · MD VIP - Utica · Osteopathic Health Care Associates · PRISM Extended Care and Urgent Care</t>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C-W7D1</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Clinton Township (3) • Sterling Heights (2) • Macomb (1)</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>R01, R06, R09, R12, R15</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Normandy Family Practice · The Family Doctor · Cornerstone Internal Medicine · Oak Street Health - Eastgate · Epic Healthcare - Southfield · Oakland Primary Care · Macomb Physicians Group · DMC Orthopedics &amp; Sports Medicine - Warren · Chronic Pain Institute · Office of George Nassif MD</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>C-R24</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Maan Askar MD - Hoover (Thursdays) · Forum Medical Clinic · Julie Henry, MD · Greater Michigan Orthopedics and Sports Medicine - Warren · Midwest Center for Dermatology - Warren · Motor City Orthopedics - Warren · Beaumont Associated Family Care - Warren · Maan Askar MD - 13 Mile</t>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C-W7D2</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>City Of The Village Of Clarkston (1) • Farmington (1) • Madison Heights (1)</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>R02, R04, R05, R17, R26, R27</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Premiere Pediatrics · Michigan Institute for Neurological Disorders (MIND) - Farmington Hills · Preferred Medical Group · Be Well Medical Center · Lakeview Medical Center · Faith Internal Medicine &amp; Urgent Care · MEDPRO PRIMARY CARE - Waltz Rd · TRENTON TOTAL HEALTH CARE CENTER, PC · Springfield Urgent Care - Hamburg · Gratiot Family Medicine</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>C-R25</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Live Well Chiro · Karle Medical Group · Michigan Center For Regenerative Medicine · Ciarlone Orthopedics · Amabir Khaira MD · Meadowbrook Internists · Barclay Internists · Rochester Hills Orthopedics &amp; Sports Medicine · Balanced Living Chiropractic · Colleen Kennedy DO</t>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C-W7D3</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Rochester Hills (4) • Sterling Heights (2) • Rochester (1)</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>R01, R22, R25</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Barclay Internists · Prism Medical Group - Family Medicine Ste 240 · Meadowbrook Internists · Prism Medical Group - Internal Medicine · Physicians in Family Medicine · Office of Steven Trombly MD · Henry Ford Macomb Internal Medicine</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>C-R01+R03+R04+R10+R15+R16+R18+R20</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Normandy Family Practice · Premier Private Physicians · Faith Internal Medicine &amp; Urgent Care · MEDPRO PRIMARY CARE - Waltz Rd · Corondan Medical · Urgent Care Family · Schoenherr Family Practice · North Valley Internal Medicine · Corewell Internal Medicine Midway · Specialists in Rehabilitation Medicine</t>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C-W7D4</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Madison Heights (1) • Warren (1) • Ferndale (1)</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>R07, R28</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Madison Medical Arts · Barry S Meyer DO PC · Epic Primary Care - Ferndale · Clarkston Medical Group</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>C-R05+R06+R07+R09+R14+R17</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>C-W8D1</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Premiere Pediatrics · Troy Primary Care · Progressive Health Care · Office of George Nassif MD · John R Medical Clinic · MHP Internal Medicine · Oak Street Health - Eastgate · Oakland Primary Care · Troy Health Center · Saurabh Gupta MD</t>
+        <v>7</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Sterling Heights (3) • St Clair Shores (1) • Troy (1)</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>R01, R02, R03, R10, R13, R14, R16, R18, R20</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Shaun Jayakar MD · Premier Private Physicians · Corondan Medical · Specialists in Rehabilitation Medicine · Rochester Medical Group · Macomb Medical Clinic · Urgent Care Family · Office of Josephine A. Iskander MD · Schoenherr Family Practice · North Valley Internal Medicine</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>C-R19</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>C-W8D2</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Brighton Internal Medicine</t>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Roseville (3) • Madison Heights (2) • New Baltimore (1)</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>R02, R05, R07, R08, R11</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Bay Area Family Physicians · Community First Health Centers - New Haven · Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD · Michigan Institute for Neurological Disorders (MIND) - Roseville · John R Medical Clinic · MHP Internal Medicine · Progressive Health Care · Premier Family Physicians · Troy Primary Care</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>C-R26</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C-W9D1</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Ruffini DC PC, Richard J · Springfield Urgent Care - Hamburg · Trinity Health System Pain Institute · Associates In Physical Medicine &amp; Rehabilitation · MICHIGAN PAIN SPECIALISTS, PLLC · Michigan Pain Specialists · Clarkston Medical Group Adult &amp; Pediatric Medicine · MOTOR CITY ORTHOPEDICS - Novi · Restorative Physical Medicine - Novi · Urgent Care of Milford</t>
+      <c r="E36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Warren (2) • Shelby Township (2) • St Clair Shores (1)</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>R09, R10, R19, R21, R23, R24, R25, R26</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Midwest Center for Dermatology - Warren · Beaumont Associated Family Care - Warren · Lakeside Internal Medicine · Colleen Kennedy DO · Associated Orthopedists of Detroit-Shelby Township · Alliance - Macomb · McLaren Oakland Center for Spine &amp; Pain Management · Clarkston Medical Group Adult &amp; Pediatric Medicine · Oakland Internal Medicine Associates - Henry Ford · Brighton Internal Medicine</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>C-R27</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>TRENTON TOTAL HEALTH CARE CENTER, PC · Blanzy Corwell clinic Southgate · MEGHA MOHEY, MD, PC · INTERNAL MEDICINE ASSOCIATES OF MICHIGAN, PC · Corewell Health Taylor Hospital Family Medicine · Great Lakes Health and Wellness · Ghassan Atto PLLC · Family Medicine · Premier Orthopedics</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>C-R01+R12+R13</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Cornerstone Internal Medicine · Epic Healthcare - Southfield · Frederick Karoub MD PC · Office of Josephine A. Iskander MD · Chronic Pain Institute · The Family Doctor · Henry Ford Macomb Internal Medicine · DMC Orthopedics &amp; Sports Medicine - Warren · Office of Steven Trombly MD · Macomb Physicians Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>C-R02+R05+R07+R11</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Premier Family Physicians · Shaun Jayakar MD · Preferred Medical Group · Be Well Medical Center · Epic Primary Care - Ferndale · Madison Medical Arts · Barry S Meyer DO PC · Henry Ford St. John Center for Wellness · Sudha Nannapaneni MD · Michigan Institute for Neurological Disorders (MIND) - Roseville</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>C-R21</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>McLaren Oakland Center for Spine &amp; Pain Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>C-R28</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Clarkston Internal Medicine · Clarkston Family Medicine · Clarkston Pain &amp; Rehab · Oakland Orthopedics &amp; Sports Medicine · Trinity IHA Primary Care - Clarkston · Clarkston Medical Group · Neuro Pain Consultants - Clarkston · MDVIP Clarkston</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>Open slot ×1</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr"/>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>Flex: backlog pull-forward · huddle promotes · ortho field day</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>C-R02+R06+R08+R09+R14+R15</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Lakeview Medical Center · Gratiot Family Medicine · Cornerstone Garfield Family Practice - Ascension · Bay Area Family Physicians · Community First Health Centers - New Haven · North Macomb Medical Associates · Lakeside Internal Medicine · Henry Ford Macomb Health Center - Fraser · Macomb Medical Clinic · EPIC Southfield - Telegraph Rd office</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>C-R04+R10+R15+R16+R22</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Neurology Consultants of Southfield · Michigan MSK Medicine - Clinton Township · Vital Medicine · GREAT LAKE PHYSICIANS, PC · Oakland Internal Medicine Associates - Henry Ford · Rochester Medical Group · Prism Medical Group - Family Medicine Ste 240 · Prism Medical Group - Internal Medicine · Physicians in Family Medicine</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>Open slot ×3</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Flex: backlog pull-forward · huddle promotes · ortho field day</t>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C-W9D2</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Clinton Township (3) • Southfield (1) • Richmond (1)</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>R06, R08, R09, R12, R15</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>EPIC Southfield - Telegraph Rd office · Michigan MSK Medicine - Clinton Township · Henry Ford Macomb Health Center - Fraser · Cornerstone Garfield Family Practice - Ascension · North Macomb Medical Associates · Frederick Karoub MD PC · Belamedica</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19352,2193 +19951,2193 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>96903a48-13a7-42e0-8f5e-a56cce365ea5</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Anchor Bay Clinic Family Medical Center</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>New Baltimore</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Now HF affiliated</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>b9b7ff1f-a14b-4733-af73-e7371152c69a</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Macomb Family Medicine (Henry Ford) - Chesterfield</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Chesterfield</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr"/>
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>1619909793</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Dennis G Kelly DO</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Madison Heights</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr"/>
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>1023116068</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Center for Preventative Medicine</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Grosse Pointe</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr"/>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>7e174398-087f-41d2-8f79-7c1a94c070e5</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Henry Ford Macomb Orthopedic Surgery - Washington</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Washington</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>66604f44-0a10-4e2a-8f1e-c4e00f0fb1dc</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Partners in Family Medicine</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Shelby Township</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr"/>
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>da7a2e70-7373-4808-9950-99c98f41d55e</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Blue Water Pain Specialists - Macomb</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Macomb</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr"/>
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>e33f4068-dcba-4ec6-a5b6-a0ce07fd66d3</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Michigan Head &amp; Spine Institute - Macomb</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Clinton Township</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr"/>
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>aaaaf0e6-b931-49ae-be22-319368bfc366</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>IHA Hand Surgery - Brighton</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>BRIGHTON</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>6abec30d-30ef-4f35-8e04-85112389bfb1</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>JOEL WELLNESS CLINIC</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Livonia</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>a320a856-33fb-458b-8907-d98101fceb1b</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Roger D Ajluni MD PC</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Livonia</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr"/>
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>7ba5f22d-a044-4e77-9eae-086d15413f50</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Beacon Orthopedics of Michigan - Livonia</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Livonia</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr"/>
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>80d59d4a-83b2-4eff-a6a5-58214e7bf1ba</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Blue Water Pain Specialists - St Clair Shores</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>St. Clair Shores</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr"/>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>96920148-57be-4764-88fe-0131ee3733e7</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Arora Hand Surgery - Warren</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Warren</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr"/>
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>1538237060</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Henry Ford Medical Center - Beck Rd</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Plymouth</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr"/>
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>1fcb9ed3-4f7b-4998-b644-3c8f0d4fefba</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>UofM Northville Health Center</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Northville</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr"/>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr"/>
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>1972528818</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Levan Internists</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Livonia</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Not my account. Being called on by Jasmine</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>Reassigned to Jasmine’s routes — pending Kristen confirmation</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>af12dee4-a837-45cd-b77e-ae4d5a1da5b3</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Primary Care Services -Westland</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Westland</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr"/>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr"/>
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>844e3cfa-90dd-4405-b93e-8ec8a51a6b23</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>MSU SportsMEDICINE</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>East Lansing</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr"/>
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>20a601f2-ef2f-40db-b5ec-481cf50305de</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Henry Ford Internal Medicine - Sterling Heights</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Sterling Heights</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr"/>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr"/>
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>c47f040d-217f-4526-bd80-92b1073a4d77</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Foot &amp; Ankle Specialists of Southeast Michigan - Warren</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>Other / Verify</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Warren</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr"/>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr"/>
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>1609867985</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Beaumont Neurosurgery</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Troy</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr"/>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr"/>
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>5bb9aa8b-846a-4a0b-ab77-289399d9b1b1</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Glowacki MD - Institute for Pain, Spine &amp; Headache Disorders</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>Troy</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr"/>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>c796443f-9c0a-4e5d-9f5a-df76d3e311bc</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Ascension Providence Partners in Womens Health</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Southfield</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr"/>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr"/>
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>2fc64685-2270-4f5f-827a-7788409cd5cd</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Pulmonary &amp; Internal Medicine Specialists</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Southfield</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr"/>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr"/>
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>15d2de97-a164-4b7e-a3a2-15673271319b</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Specialists in Spine Surgery - Garden City</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>Garden City</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr"/>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr"/>
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>0c7e4fda-32b4-4999-afc5-3ead3985f8c9</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Michigan Orthopaedic &amp; Spine Surgeons</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr"/>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr"/>
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>d606572a-912c-4bad-b906-c9a8d0479eff</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Clarkston Medical Group - Oxford</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>OXFORD</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr"/>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr"/>
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>172f7e80-1532-4f45-8c82-d3d09547c86d</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>David S Hollett MD</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr"/>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr"/>
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>118d4718-8c24-42b0-ae12-a1975f146750</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Henry Ford Macomb Orthopedics - Chesterfield</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>Chesterfield</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr"/>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr"/>
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>1275554073</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Chesterfield Family Medicine (Henry Ford)</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>New Baltimore</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr"/>
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>d361f230-715e-4c7e-87a9-bf50246f42f4</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Eastside Neurosurgery - Macomb</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>Macomb</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr"/>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr"/>
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>a2352347-063f-4a39-a0c1-25774fd3490b</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Michigan Head &amp; Spine Institute - Novi</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>Novi</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr"/>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>1244d3ff-0839-4759-af42-e22dd1c77549</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Niva Health</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>Novi</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr"/>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr"/>
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>989f0eea-dc08-4445-9a51-ee7663255964</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Michigan Spine Institute</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>Waterford Township</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr"/>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr"/>
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>d52215b9-d874-4639-9ff2-a87b853ad52d</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Adult Wellness &amp; Internal Medicine</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Flint</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr"/>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr"/>
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>4dd7647d-ac5e-4f26-a696-b59cd2cfb219</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Mid-Michigan Pain Specialty</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>Flint</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr"/>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>1235110537</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Ortho Michigan - Flint</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>Flint</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr"/>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr"/>
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>74360f7a-f042-4521-a7bb-a807dcb10282</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Advance Urgent Care - Hartland</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>Urgent Care</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>Hartland</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr"/>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>a29bc662-1f09-48ea-a1f5-efe24cc01eeb</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Great Lakes Medicine</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>ER / Hospital</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>Shelby Twp</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr"/>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr"/>
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>3bfd16c2-8d66-4fed-9ad2-cc715dfd2eb8</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>Revolution Wellness</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>Utica</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr"/>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>4d38264b-b17e-42b4-9043-92ff06e62c09</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>WARREN PODIATRY</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Other / Verify</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>WARREN</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr"/>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr"/>
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>c2e9f4c4-65ff-4730-abe0-7f210be0bf8f</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>Michigan Brain &amp; Spine - Warren</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Warren</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr"/>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr"/>
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>9b6db0bd-31b4-4d7e-b351-e4ee78a4defa</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>Trinity IHA Primary Care - Rochester Hills</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr"/>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr"/>
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>7c9505b8-9a32-47d6-a489-6171ce848c9e</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>LMT Rehabilitation Associates - Troy</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>Troy</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr"/>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>c48a8a2e-4d60-4a18-8000-3f3dea9cf03a</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>DEVYANI KHAMBETE, MD, PC</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>WATERFORD</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr"/>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>ff09ce61-5da4-4d5d-9ae6-7b9215731ce9</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>McLaren Center for Spine &amp; Pain Management</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t>Clinton Township</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr"/>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr"/>
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>4d131d76-2f91-472e-bf42-c1ae3f5f7622</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>McLaren Macomb Family First</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>Clinton Township</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr"/>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr"/>
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>f5b10e96-2444-4c72-b938-1004495c7ee3</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Ernest Chiodo MD</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>CLINTON TOWNSHIP</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr"/>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>54898915-220c-4900-ba07-febdcdb005c0</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Edward A. Tashjian, MD - Clarkston</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>City of the Village of Clarkston</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr"/>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr"/>
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>e0f2c54e-06ee-4e34-863e-cb4675bd5c6e</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>PINE TREE MEDICAL CENTER</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>WATERFORD</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr"/>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>c3b6301b-b3bc-474d-9ddd-d21fd2c40797</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>Health First Medical Center</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>SOUTHGATE</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr"/>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>aaded854-5fe8-4282-b99d-3af289b977e0</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Back &amp; Pain Center (UofM) at Burlington Bldg</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>Ann Arbor</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr"/>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>4430ce9a-04c4-4489-8cd4-1f4abdc28ce9</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>U of M Physical Medicine &amp; Rehabilitation Clinic - Burlington Building</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>Ann Arbor</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr"/>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr"/>
+      <c r="G56" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>c357306a-7118-459d-82fc-5365721ca926</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>U of M Neurosurgery</t>
         </is>
       </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr">
         <is>
           <t>Ann Arbor</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr"/>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr"/>
+      <c r="G57" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>6900d9f0-9d28-423a-98a4-281fb9ac13c1</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>IHA Ann Arbor Orthpaedic Specialists</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>Ypsilanti</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr"/>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr"/>
+      <c r="G58" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>b6be5dd0-40a2-450c-946b-5deaaf8b0178</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>Trinity IHA Hand Surgery - Ypsilanti</t>
         </is>
       </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>Ypsilanti</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr"/>
-      <c r="G59" s="12" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr"/>
+      <c r="G59" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>19d50314-6b7d-4516-94cb-e3c191c3fde1</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>MedSport - Ann Arbor Domino's Farms</t>
         </is>
       </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E60" s="10" t="inlineStr">
         <is>
           <t>Ann Arbor</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr"/>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr"/>
+      <c r="G60" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>42caeada-e3af-49fd-ab98-cc39cf1a5ffe</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>Chelsea Physical Medicine &amp; Rehabilitation Specialists</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>Chelsea</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr"/>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr"/>
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>1033228903</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>Trinity Health IHA Orthopaedics - Chelsea</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>Chelsea</t>
         </is>
       </c>
-      <c r="F62" s="12" t="inlineStr"/>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr"/>
+      <c r="G62" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>e73e7e8b-2c72-479d-b015-c7ff5509f700</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>Precision Interventional Radiology</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>FARMINGTON HILLS</t>
         </is>
       </c>
-      <c r="F63" s="12" t="inlineStr"/>
-      <c r="G63" s="12" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>2b5bba73-5878-4fa6-b615-7b5106bbe4e0</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>SPINE SPECIALISTS OF MICHIGAN, PC</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>BINGHAM FARMS</t>
         </is>
       </c>
-      <c r="F64" s="12" t="inlineStr"/>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr"/>
+      <c r="G64" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>1619959566</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>Beaumont Royal Oak - Physical Medicine &amp; Rehabilitation</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>Royal Oak</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr"/>
-      <c r="G65" s="12" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr"/>
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>4c1b7fe8-a5c4-417f-bee6-92fae75a3c35</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>Spine &amp; Brain Surgery Specialists</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>Royal Oak</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr"/>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr"/>
+      <c r="G66" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>d012f6c8-f44d-46a5-9f8e-b3b522de7d83</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>Arthritis Physicians</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E67" s="11" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr"/>
-      <c r="G67" s="12" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr"/>
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>47bcf8c4-c5dc-4d5a-9a9e-4bece6e01698</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>Premier Surgical Specialists</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>Pain</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>Rochester Hills</t>
         </is>
       </c>
-      <c r="F68" s="12" t="inlineStr"/>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr"/>
+      <c r="G68" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>Your 82 “Not sure” rows stay in the routes (amber in Stops tab) and go to the Jul 31 consolidation with Joel — they are NOT removed.</t>
         </is>
